--- a/fichiers_csv/poules_senior_masculin1.xlsx
+++ b/fichiers_csv/poules_senior_masculin1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\L3\TER_2026_Constitution_de_poules_sportives\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Downloads\L3\TER_2026_Constitution_de_poules_sportives\fichiers_csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6761D478-5CEC-4A66-8E1E-7CBE1D43FBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB987399-E7CE-4EFE-BCDC-E5EAB1CF3872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2124" yWindow="2124" windowWidth="20856" windowHeight="8964" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Niveau 1" sheetId="1" r:id="rId1"/>
@@ -1019,9 +1019,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1520,19 +1519,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.796875" customWidth="1"/>
     <col min="2" max="2" width="20.796875" customWidth="1"/>
     <col min="3" max="3" width="22.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1543,7 +1542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1554,7 +1553,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1565,7 +1564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1576,7 +1575,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1587,7 +1586,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1598,7 +1597,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1609,7 +1608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1620,7 +1619,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1631,7 +1630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1642,7 +1641,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1653,7 +1652,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1664,7 +1663,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1675,7 +1674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1686,7 +1685,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1697,7 +1696,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1708,7 +1707,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1719,7 +1718,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1730,7 +1729,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>46</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1752,7 +1751,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -1763,7 +1762,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1774,7 +1773,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1785,7 +1784,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1796,7 +1795,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -1807,7 +1806,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>62</v>
       </c>
@@ -1818,7 +1817,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>64</v>
       </c>
@@ -1829,7 +1828,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -1840,7 +1839,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -1851,7 +1850,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1862,7 +1861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -1873,7 +1872,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -1884,7 +1883,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -1895,7 +1894,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>76</v>
       </c>
@@ -1906,7 +1905,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>78</v>
       </c>
@@ -1917,7 +1916,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -1928,7 +1927,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1939,7 +1938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>83</v>
       </c>
@@ -1950,7 +1949,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -1961,7 +1960,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>87</v>
       </c>
@@ -1972,7 +1971,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>89</v>
       </c>
@@ -1983,7 +1982,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -1994,7 +1993,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>93</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -2016,7 +2015,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>95</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>97</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>99</v>
       </c>
@@ -2049,7 +2048,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>101</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>103</v>
       </c>
@@ -2071,7 +2070,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>105</v>
       </c>
@@ -2082,7 +2081,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -2093,7 +2092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>107</v>
       </c>
@@ -2104,7 +2103,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>109</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>111</v>
       </c>
@@ -2126,7 +2125,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>113</v>
       </c>
@@ -2137,7 +2136,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>115</v>
       </c>
@@ -2159,19 +2158,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C71"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.796875" customWidth="1"/>
     <col min="2" max="2" width="20.796875" customWidth="1"/>
     <col min="3" max="3" width="22.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2193,7 +2192,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2204,7 +2203,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2215,7 +2214,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -2226,7 +2225,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -2237,7 +2236,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -2248,7 +2247,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -2259,7 +2258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -2281,7 +2280,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -2292,7 +2291,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -2303,7 +2302,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -2314,7 +2313,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -2325,7 +2324,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -2336,7 +2335,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2347,7 +2346,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -2358,7 +2357,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -2369,7 +2368,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2380,7 +2379,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2391,7 +2390,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -2402,7 +2401,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -2413,7 +2412,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>115</v>
       </c>
@@ -2424,7 +2423,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -2446,7 +2445,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -2457,7 +2456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -2468,7 +2467,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -2479,7 +2478,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>113</v>
       </c>
@@ -2490,7 +2489,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -2501,7 +2500,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -2512,7 +2511,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -2523,7 +2522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>85</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -2545,7 +2544,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>89</v>
       </c>
@@ -2556,7 +2555,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2567,7 +2566,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>93</v>
       </c>
@@ -2578,7 +2577,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -2589,7 +2588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -2600,7 +2599,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -2611,7 +2610,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>99</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>101</v>
       </c>
@@ -2633,7 +2632,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>105</v>
       </c>
@@ -2644,7 +2643,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -2655,7 +2654,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -2666,7 +2665,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -2677,7 +2676,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>16</v>
       </c>
@@ -2688,7 +2687,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -2699,7 +2698,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>152</v>
       </c>
@@ -2710,7 +2709,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -2721,7 +2720,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -2743,7 +2742,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -2754,7 +2753,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -2765,7 +2764,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>158</v>
       </c>
@@ -2776,7 +2775,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -2787,7 +2786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>43</v>
       </c>
@@ -2798,7 +2797,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2809,7 +2808,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>27</v>
       </c>
@@ -2820,7 +2819,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>30</v>
       </c>
@@ -2842,19 +2841,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.796875" customWidth="1"/>
     <col min="2" max="2" width="20.796875" customWidth="1"/>
     <col min="3" max="3" width="22.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2865,7 +2864,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2876,7 +2875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2887,7 +2886,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -2898,7 +2897,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>111</v>
       </c>
@@ -2909,7 +2908,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>113</v>
       </c>
@@ -2920,7 +2919,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -2931,7 +2930,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -2942,7 +2941,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -2953,7 +2952,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -2964,7 +2963,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -2975,7 +2974,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -2986,7 +2985,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>99</v>
       </c>
@@ -2997,7 +2996,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -3008,7 +3007,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -3019,7 +3018,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -3030,7 +3029,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -3041,7 +3040,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>72</v>
       </c>
@@ -3052,7 +3051,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -3074,7 +3073,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -3085,7 +3084,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -3096,7 +3095,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -3107,7 +3106,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -3118,7 +3117,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>43</v>
       </c>
@@ -3129,7 +3128,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -3140,7 +3139,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>115</v>
       </c>
@@ -3151,7 +3150,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>55</v>
       </c>
@@ -3162,7 +3161,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -3173,7 +3172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -3184,7 +3183,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>97</v>
       </c>
@@ -3195,7 +3194,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -3206,7 +3205,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>103</v>
       </c>
@@ -3217,7 +3216,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -3228,7 +3227,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>49</v>
       </c>
@@ -3239,7 +3238,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>68</v>
       </c>
@@ -3261,7 +3260,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -3272,7 +3271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -3283,7 +3282,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>85</v>
       </c>
@@ -3294,7 +3293,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>89</v>
       </c>
@@ -3305,7 +3304,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>78</v>
       </c>
@@ -3316,7 +3315,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -3327,7 +3326,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -3338,7 +3337,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>81</v>
       </c>
@@ -3349,7 +3348,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -3360,7 +3359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>109</v>
       </c>
@@ -3371,7 +3370,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>87</v>
       </c>
@@ -3382,7 +3381,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -3393,7 +3392,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -3404,7 +3403,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>91</v>
       </c>
@@ -3415,7 +3414,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>16</v>
       </c>
@@ -3437,19 +3436,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C71"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.796875" customWidth="1"/>
     <col min="2" max="2" width="20.796875" customWidth="1"/>
     <col min="3" max="3" width="22.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3460,7 +3459,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -3471,7 +3470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -3482,7 +3481,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3493,7 +3492,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -3504,7 +3503,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -3515,7 +3514,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -3526,7 +3525,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -3537,7 +3536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -3548,7 +3547,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -3559,7 +3558,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -3570,7 +3569,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -3581,7 +3580,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -3592,7 +3591,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -3603,7 +3602,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -3625,7 +3624,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -3636,7 +3635,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3647,7 +3646,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -3658,7 +3657,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -3669,7 +3668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -3680,7 +3679,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -3691,7 +3690,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>115</v>
       </c>
@@ -3702,7 +3701,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -3713,7 +3712,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -3724,7 +3723,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -3735,7 +3734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -3746,7 +3745,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -3757,7 +3756,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>113</v>
       </c>
@@ -3768,7 +3767,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -3779,7 +3778,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -3790,7 +3789,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -3801,7 +3800,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>85</v>
       </c>
@@ -3812,7 +3811,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -3823,7 +3822,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>89</v>
       </c>
@@ -3834,7 +3833,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -3845,7 +3844,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>93</v>
       </c>
@@ -3856,7 +3855,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -3867,7 +3866,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -3878,7 +3877,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -3889,7 +3888,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>99</v>
       </c>
@@ -3900,7 +3899,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>101</v>
       </c>
@@ -3911,7 +3910,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>105</v>
       </c>
@@ -3922,7 +3921,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -3933,7 +3932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>107</v>
       </c>
@@ -3944,7 +3943,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -3955,7 +3954,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>16</v>
       </c>
@@ -3966,7 +3965,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -3977,7 +3976,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>152</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -3999,7 +3998,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>70</v>
       </c>
@@ -4010,7 +4009,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>66</v>
       </c>
@@ -4021,7 +4020,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -4032,7 +4031,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -4043,7 +4042,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>158</v>
       </c>
@@ -4054,7 +4053,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -4065,7 +4064,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>43</v>
       </c>
@@ -4076,7 +4075,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -4087,7 +4086,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>27</v>
       </c>
@@ -4098,7 +4097,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>30</v>
       </c>
@@ -4242,2138 +4241,2138 @@
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>265</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>266</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>267</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>268</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>269</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>270</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
         <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>271</v>
       </c>
       <c r="N2">
         <v>1</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="O2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" t="s">
+        <v>2</v>
+      </c>
+      <c r="X2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>265</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>266</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>267</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>268</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>272</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>273</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="H3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" t="s">
         <v>2</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" t="s">
         <v>271</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC3" s="1" t="s">
+      <c r="O3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>2</v>
+      </c>
+      <c r="R3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" t="s">
+        <v>2</v>
+      </c>
+      <c r="U3" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" t="s">
+        <v>2</v>
+      </c>
+      <c r="X3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>265</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>266</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>267</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>268</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>274</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>275</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" t="s">
         <v>2</v>
       </c>
       <c r="L4">
         <v>1</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" t="s">
         <v>276</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="1" t="s">
+      <c r="O4" t="s">
+        <v>2</v>
+      </c>
+      <c r="P4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>2</v>
+      </c>
+      <c r="R4" t="s">
+        <v>2</v>
+      </c>
+      <c r="S4" t="s">
+        <v>2</v>
+      </c>
+      <c r="T4" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" t="s">
+        <v>2</v>
+      </c>
+      <c r="V4" t="s">
+        <v>2</v>
+      </c>
+      <c r="W4" t="s">
+        <v>2</v>
+      </c>
+      <c r="X4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>265</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>266</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>267</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>268</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>277</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" t="s">
         <v>278</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="H5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
         <v>2</v>
       </c>
       <c r="L5">
         <v>1</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" t="s">
         <v>271</v>
       </c>
       <c r="N5">
         <v>1</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC5" s="1" t="s">
+      <c r="O5" t="s">
+        <v>2</v>
+      </c>
+      <c r="P5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>2</v>
+      </c>
+      <c r="R5" t="s">
+        <v>2</v>
+      </c>
+      <c r="S5" t="s">
+        <v>2</v>
+      </c>
+      <c r="T5" t="s">
+        <v>2</v>
+      </c>
+      <c r="U5" t="s">
+        <v>2</v>
+      </c>
+      <c r="V5" t="s">
+        <v>2</v>
+      </c>
+      <c r="W5" t="s">
+        <v>2</v>
+      </c>
+      <c r="X5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>265</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>266</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>267</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>268</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>279</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" t="s">
         <v>280</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="H6" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
         <v>2</v>
       </c>
       <c r="L6">
         <v>3</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" t="s">
         <v>271</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="1" t="s">
+      <c r="O6" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R6" t="s">
+        <v>2</v>
+      </c>
+      <c r="S6" t="s">
+        <v>2</v>
+      </c>
+      <c r="T6" t="s">
+        <v>2</v>
+      </c>
+      <c r="U6" t="s">
+        <v>2</v>
+      </c>
+      <c r="V6" t="s">
+        <v>2</v>
+      </c>
+      <c r="W6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>265</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>266</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>267</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>268</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>281</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" t="s">
         <v>282</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
         <v>2</v>
       </c>
       <c r="L7">
         <v>1</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" t="s">
         <v>271</v>
       </c>
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="1" t="s">
+      <c r="O7" t="s">
+        <v>2</v>
+      </c>
+      <c r="P7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R7" t="s">
+        <v>2</v>
+      </c>
+      <c r="S7" t="s">
+        <v>2</v>
+      </c>
+      <c r="T7" t="s">
+        <v>2</v>
+      </c>
+      <c r="U7" t="s">
+        <v>2</v>
+      </c>
+      <c r="V7" t="s">
+        <v>2</v>
+      </c>
+      <c r="W7" t="s">
+        <v>2</v>
+      </c>
+      <c r="X7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>265</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>266</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>267</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>268</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>283</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" t="s">
         <v>284</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="H8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>2</v>
+      </c>
+      <c r="K8" t="s">
         <v>2</v>
       </c>
       <c r="L8">
         <v>1</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" t="s">
         <v>271</v>
       </c>
       <c r="N8">
         <v>1</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="1" t="s">
+      <c r="O8" t="s">
+        <v>2</v>
+      </c>
+      <c r="P8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>2</v>
+      </c>
+      <c r="R8" t="s">
+        <v>2</v>
+      </c>
+      <c r="S8" t="s">
+        <v>2</v>
+      </c>
+      <c r="T8" t="s">
+        <v>2</v>
+      </c>
+      <c r="U8" t="s">
+        <v>2</v>
+      </c>
+      <c r="V8" t="s">
+        <v>2</v>
+      </c>
+      <c r="W8" t="s">
+        <v>2</v>
+      </c>
+      <c r="X8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC8" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>265</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>266</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>267</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>268</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>285</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" t="s">
         <v>286</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="H9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" t="s">
         <v>2</v>
       </c>
       <c r="L9">
         <v>1</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" t="s">
         <v>276</v>
       </c>
       <c r="N9">
         <v>1</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="1" t="s">
+      <c r="O9" t="s">
+        <v>2</v>
+      </c>
+      <c r="P9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>2</v>
+      </c>
+      <c r="R9" t="s">
+        <v>2</v>
+      </c>
+      <c r="S9" t="s">
+        <v>2</v>
+      </c>
+      <c r="T9" t="s">
+        <v>2</v>
+      </c>
+      <c r="U9" t="s">
+        <v>2</v>
+      </c>
+      <c r="V9" t="s">
+        <v>2</v>
+      </c>
+      <c r="W9" t="s">
+        <v>2</v>
+      </c>
+      <c r="X9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC9" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>265</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>267</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>268</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>285</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" t="s">
         <v>286</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="H10" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" t="s">
         <v>2</v>
       </c>
       <c r="L10">
         <v>2</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" t="s">
         <v>271</v>
       </c>
       <c r="N10">
         <v>1</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC10" s="1" t="s">
+      <c r="O10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>2</v>
+      </c>
+      <c r="R10" t="s">
+        <v>2</v>
+      </c>
+      <c r="S10" t="s">
+        <v>2</v>
+      </c>
+      <c r="T10" t="s">
+        <v>2</v>
+      </c>
+      <c r="U10" t="s">
+        <v>2</v>
+      </c>
+      <c r="V10" t="s">
+        <v>2</v>
+      </c>
+      <c r="W10" t="s">
+        <v>2</v>
+      </c>
+      <c r="X10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>265</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>266</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>267</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>268</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>287</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" t="s">
         <v>288</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="H11" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
         <v>2</v>
       </c>
       <c r="L11">
         <v>1</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" t="s">
         <v>271</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC11" s="1" t="s">
+      <c r="O11" t="s">
+        <v>2</v>
+      </c>
+      <c r="P11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>2</v>
+      </c>
+      <c r="R11" t="s">
+        <v>2</v>
+      </c>
+      <c r="S11" t="s">
+        <v>2</v>
+      </c>
+      <c r="T11" t="s">
+        <v>2</v>
+      </c>
+      <c r="U11" t="s">
+        <v>2</v>
+      </c>
+      <c r="V11" t="s">
+        <v>2</v>
+      </c>
+      <c r="W11" t="s">
+        <v>2</v>
+      </c>
+      <c r="X11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>265</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>266</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>267</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>268</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>289</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" t="s">
         <v>290</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="H12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
         <v>2</v>
       </c>
       <c r="L12">
         <v>1</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" t="s">
         <v>276</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC12" s="1" t="s">
+      <c r="O12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>2</v>
+      </c>
+      <c r="R12" t="s">
+        <v>2</v>
+      </c>
+      <c r="S12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T12" t="s">
+        <v>2</v>
+      </c>
+      <c r="U12" t="s">
+        <v>2</v>
+      </c>
+      <c r="V12" t="s">
+        <v>2</v>
+      </c>
+      <c r="W12" t="s">
+        <v>2</v>
+      </c>
+      <c r="X12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>265</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>266</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>267</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>268</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>291</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" t="s">
         <v>292</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" t="s">
         <v>5</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K13" s="1" t="s">
+      <c r="H13" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
         <v>2</v>
       </c>
       <c r="L13">
         <v>1</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" t="s">
         <v>271</v>
       </c>
       <c r="N13">
         <v>1</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC13" s="1" t="s">
+      <c r="O13" t="s">
+        <v>2</v>
+      </c>
+      <c r="P13" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>2</v>
+      </c>
+      <c r="R13" t="s">
+        <v>2</v>
+      </c>
+      <c r="S13" t="s">
+        <v>2</v>
+      </c>
+      <c r="T13" t="s">
+        <v>2</v>
+      </c>
+      <c r="U13" t="s">
+        <v>2</v>
+      </c>
+      <c r="V13" t="s">
+        <v>2</v>
+      </c>
+      <c r="W13" t="s">
+        <v>2</v>
+      </c>
+      <c r="X13" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>265</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>266</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>267</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>268</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>293</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" t="s">
         <v>294</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K14" s="1" t="s">
+      <c r="H14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" t="s">
         <v>2</v>
       </c>
       <c r="L14">
         <v>1</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" t="s">
         <v>271</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC14" s="1" t="s">
+      <c r="O14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P14" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>2</v>
+      </c>
+      <c r="R14" t="s">
+        <v>2</v>
+      </c>
+      <c r="S14" t="s">
+        <v>2</v>
+      </c>
+      <c r="T14" t="s">
+        <v>2</v>
+      </c>
+      <c r="U14" t="s">
+        <v>2</v>
+      </c>
+      <c r="V14" t="s">
+        <v>2</v>
+      </c>
+      <c r="W14" t="s">
+        <v>2</v>
+      </c>
+      <c r="X14" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>265</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>266</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>267</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>268</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" t="s">
         <v>295</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" t="s">
         <v>296</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="H15" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" t="s">
         <v>2</v>
       </c>
       <c r="L15">
         <v>1</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" t="s">
         <v>271</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC15" s="1" t="s">
+      <c r="O15" t="s">
+        <v>2</v>
+      </c>
+      <c r="P15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>2</v>
+      </c>
+      <c r="R15" t="s">
+        <v>2</v>
+      </c>
+      <c r="S15" t="s">
+        <v>2</v>
+      </c>
+      <c r="T15" t="s">
+        <v>2</v>
+      </c>
+      <c r="U15" t="s">
+        <v>2</v>
+      </c>
+      <c r="V15" t="s">
+        <v>2</v>
+      </c>
+      <c r="W15" t="s">
+        <v>2</v>
+      </c>
+      <c r="X15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC15" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>265</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>266</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>267</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>268</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>297</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" t="s">
         <v>298</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="H16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" t="s">
         <v>2</v>
       </c>
       <c r="L16">
         <v>1</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" t="s">
         <v>276</v>
       </c>
       <c r="N16">
         <v>1</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC16" s="1" t="s">
+      <c r="O16" t="s">
+        <v>2</v>
+      </c>
+      <c r="P16" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>2</v>
+      </c>
+      <c r="R16" t="s">
+        <v>2</v>
+      </c>
+      <c r="S16" t="s">
+        <v>2</v>
+      </c>
+      <c r="T16" t="s">
+        <v>2</v>
+      </c>
+      <c r="U16" t="s">
+        <v>2</v>
+      </c>
+      <c r="V16" t="s">
+        <v>2</v>
+      </c>
+      <c r="W16" t="s">
+        <v>2</v>
+      </c>
+      <c r="X16" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>265</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>266</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>267</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>268</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>297</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
         <v>298</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K17" s="1" t="s">
+      <c r="H17" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2</v>
+      </c>
+      <c r="K17" t="s">
         <v>2</v>
       </c>
       <c r="L17">
         <v>2</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" t="s">
         <v>271</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC17" s="1" t="s">
+      <c r="O17" t="s">
+        <v>2</v>
+      </c>
+      <c r="P17" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>2</v>
+      </c>
+      <c r="R17" t="s">
+        <v>2</v>
+      </c>
+      <c r="S17" t="s">
+        <v>2</v>
+      </c>
+      <c r="T17" t="s">
+        <v>2</v>
+      </c>
+      <c r="U17" t="s">
+        <v>2</v>
+      </c>
+      <c r="V17" t="s">
+        <v>2</v>
+      </c>
+      <c r="W17" t="s">
+        <v>2</v>
+      </c>
+      <c r="X17" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>265</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>266</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>267</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>268</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>299</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" t="s">
         <v>300</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="H18" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>2</v>
+      </c>
+      <c r="K18" t="s">
         <v>2</v>
       </c>
       <c r="L18">
         <v>1</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="M18" t="s">
         <v>271</v>
       </c>
       <c r="N18">
         <v>1</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC18" s="1" t="s">
+      <c r="O18" t="s">
+        <v>2</v>
+      </c>
+      <c r="P18" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>2</v>
+      </c>
+      <c r="R18" t="s">
+        <v>2</v>
+      </c>
+      <c r="S18" t="s">
+        <v>2</v>
+      </c>
+      <c r="T18" t="s">
+        <v>2</v>
+      </c>
+      <c r="U18" t="s">
+        <v>2</v>
+      </c>
+      <c r="V18" t="s">
+        <v>2</v>
+      </c>
+      <c r="W18" t="s">
+        <v>2</v>
+      </c>
+      <c r="X18" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>265</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>266</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>267</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>268</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>301</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" t="s">
         <v>302</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" t="s">
         <v>303</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J19" s="1" t="s">
+      <c r="H19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
         <v>304</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" t="s">
         <v>305</v>
       </c>
       <c r="L19">
         <v>1</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="M19" t="s">
         <v>271</v>
       </c>
       <c r="N19">
         <v>1</v>
       </c>
-      <c r="O19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC19" s="1" t="s">
+      <c r="O19" t="s">
+        <v>2</v>
+      </c>
+      <c r="P19" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>2</v>
+      </c>
+      <c r="R19" t="s">
+        <v>2</v>
+      </c>
+      <c r="S19" t="s">
+        <v>2</v>
+      </c>
+      <c r="T19" t="s">
+        <v>2</v>
+      </c>
+      <c r="U19" t="s">
+        <v>2</v>
+      </c>
+      <c r="V19" t="s">
+        <v>2</v>
+      </c>
+      <c r="W19" t="s">
+        <v>2</v>
+      </c>
+      <c r="X19" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC19" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" t="s">
         <v>265</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>266</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>267</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" t="s">
         <v>268</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" t="s">
         <v>301</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" t="s">
         <v>302</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="H20" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" t="s">
         <v>2</v>
       </c>
       <c r="L20">
         <v>1</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="M20" t="s">
         <v>276</v>
       </c>
       <c r="N20">
         <v>1</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC20" s="1" t="s">
+      <c r="O20" t="s">
+        <v>2</v>
+      </c>
+      <c r="P20" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>2</v>
+      </c>
+      <c r="R20" t="s">
+        <v>2</v>
+      </c>
+      <c r="S20" t="s">
+        <v>2</v>
+      </c>
+      <c r="T20" t="s">
+        <v>2</v>
+      </c>
+      <c r="U20" t="s">
+        <v>2</v>
+      </c>
+      <c r="V20" t="s">
+        <v>2</v>
+      </c>
+      <c r="W20" t="s">
+        <v>2</v>
+      </c>
+      <c r="X20" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC20" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" t="s">
         <v>265</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>266</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>267</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" t="s">
         <v>268</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" t="s">
         <v>306</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" t="s">
         <v>307</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" t="s">
         <v>5</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K21" s="1" t="s">
+      <c r="H21" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" t="s">
+        <v>2</v>
+      </c>
+      <c r="K21" t="s">
         <v>2</v>
       </c>
       <c r="L21">
         <v>1</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" t="s">
         <v>271</v>
       </c>
       <c r="N21">
         <v>1</v>
       </c>
-      <c r="O21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="1" t="s">
+      <c r="O21" t="s">
+        <v>2</v>
+      </c>
+      <c r="P21" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>2</v>
+      </c>
+      <c r="R21" t="s">
+        <v>2</v>
+      </c>
+      <c r="S21" t="s">
+        <v>2</v>
+      </c>
+      <c r="T21" t="s">
+        <v>2</v>
+      </c>
+      <c r="U21" t="s">
+        <v>2</v>
+      </c>
+      <c r="V21" t="s">
+        <v>2</v>
+      </c>
+      <c r="W21" t="s">
+        <v>2</v>
+      </c>
+      <c r="X21" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" t="s">
         <v>265</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>266</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>267</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" t="s">
         <v>268</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" t="s">
         <v>308</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" t="s">
         <v>309</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>2</v>
+      </c>
+      <c r="K22" t="s">
         <v>2</v>
       </c>
       <c r="L22">
         <v>1</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" t="s">
         <v>271</v>
       </c>
       <c r="N22">
         <v>1</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC22" s="1" t="s">
+      <c r="O22" t="s">
+        <v>2</v>
+      </c>
+      <c r="P22" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>2</v>
+      </c>
+      <c r="R22" t="s">
+        <v>2</v>
+      </c>
+      <c r="S22" t="s">
+        <v>2</v>
+      </c>
+      <c r="T22" t="s">
+        <v>2</v>
+      </c>
+      <c r="U22" t="s">
+        <v>2</v>
+      </c>
+      <c r="V22" t="s">
+        <v>2</v>
+      </c>
+      <c r="W22" t="s">
+        <v>2</v>
+      </c>
+      <c r="X22" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" t="s">
         <v>265</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>266</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
         <v>267</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" t="s">
         <v>268</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" t="s">
         <v>310</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" t="s">
         <v>311</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K23" s="1" t="s">
+      <c r="H23" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" t="s">
+        <v>2</v>
+      </c>
+      <c r="K23" t="s">
         <v>2</v>
       </c>
       <c r="L23">
         <v>1</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="M23" t="s">
         <v>276</v>
       </c>
       <c r="N23">
         <v>1</v>
       </c>
-      <c r="O23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC23" s="1" t="s">
+      <c r="O23" t="s">
+        <v>2</v>
+      </c>
+      <c r="P23" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>2</v>
+      </c>
+      <c r="R23" t="s">
+        <v>2</v>
+      </c>
+      <c r="S23" t="s">
+        <v>2</v>
+      </c>
+      <c r="T23" t="s">
+        <v>2</v>
+      </c>
+      <c r="U23" t="s">
+        <v>2</v>
+      </c>
+      <c r="V23" t="s">
+        <v>2</v>
+      </c>
+      <c r="W23" t="s">
+        <v>2</v>
+      </c>
+      <c r="X23" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC23" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" t="s">
         <v>265</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>266</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>267</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>268</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" t="s">
         <v>312</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" t="s">
         <v>313</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" t="s">
         <v>5</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="H24" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" t="s">
+        <v>2</v>
+      </c>
+      <c r="J24" t="s">
+        <v>2</v>
+      </c>
+      <c r="K24" t="s">
         <v>2</v>
       </c>
       <c r="L24">
         <v>1</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="M24" t="s">
         <v>271</v>
       </c>
       <c r="N24">
         <v>1</v>
       </c>
-      <c r="O24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC24" s="1" t="s">
+      <c r="O24" t="s">
+        <v>2</v>
+      </c>
+      <c r="P24" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>2</v>
+      </c>
+      <c r="R24" t="s">
+        <v>2</v>
+      </c>
+      <c r="S24" t="s">
+        <v>2</v>
+      </c>
+      <c r="T24" t="s">
+        <v>2</v>
+      </c>
+      <c r="U24" t="s">
+        <v>2</v>
+      </c>
+      <c r="V24" t="s">
+        <v>2</v>
+      </c>
+      <c r="W24" t="s">
+        <v>2</v>
+      </c>
+      <c r="X24" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC24" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" t="s">
         <v>265</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>266</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" t="s">
         <v>267</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>268</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" t="s">
         <v>314</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" t="s">
         <v>315</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K25" s="1" t="s">
+      <c r="H25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
         <v>2</v>
       </c>
       <c r="L25">
         <v>8</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M25" t="s">
         <v>271</v>
       </c>
       <c r="N25">
         <v>1</v>
       </c>
-      <c r="O25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC25" s="1" t="s">
+      <c r="O25" t="s">
+        <v>2</v>
+      </c>
+      <c r="P25" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>2</v>
+      </c>
+      <c r="R25" t="s">
+        <v>2</v>
+      </c>
+      <c r="S25" t="s">
+        <v>2</v>
+      </c>
+      <c r="T25" t="s">
+        <v>2</v>
+      </c>
+      <c r="U25" t="s">
+        <v>2</v>
+      </c>
+      <c r="V25" t="s">
+        <v>2</v>
+      </c>
+      <c r="W25" t="s">
+        <v>2</v>
+      </c>
+      <c r="X25" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC25" t="s">
         <v>2</v>
       </c>
     </row>
@@ -6388,7 +6387,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.796875" customWidth="1"/>
     <col min="3" max="3" width="13.796875" customWidth="1"/>
@@ -6397,12 +6396,12 @@
     <col min="7" max="7" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>213</v>
       </c>
@@ -6425,7 +6424,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>220</v>
       </c>
@@ -6448,7 +6447,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>225</v>
       </c>
@@ -6471,7 +6470,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>230</v>
       </c>
@@ -6494,7 +6493,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>235</v>
       </c>
